--- a/astro-site/public/dl/ice-cream-shop-checklist-templates/03-ice-cream-shop-manager-checklist.xlsx
+++ b/astro-site/public/dl/ice-cream-shop-checklist-templates/03-ice-cream-shop-manager-checklist.xlsx
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Calculate weekly food cost: target &lt;28–32%</t>
+          <t>Calculate weekly food cost: target 28–32% or lower</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Check expiry dates in storage and freezers (FIFO) — log reading: ____ °F</t>
+          <t>Check expiry dates in storage and freezers (FIFO)</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
